--- a/backtest_runs/20260410_193731/by_symbol/MUREB/MUREB.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MUREB/MUREB.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -587,7 +587,7 @@
         <v>-582.6600000000021</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>99417.34</v>
@@ -633,7 +633,7 @@
         <v>-1181.700000000003</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98235.64</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>98235.64</v>
@@ -725,7 +725,7 @@
         <v>-442.2599999999968</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>97793.38</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>98337.42999999999</v>
@@ -863,7 +863,7 @@
         <v>-1242.54</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>97094.89</v>
@@ -909,7 +909,7 @@
         <v>-1985.490000000003</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>95109.39999999999</v>
@@ -1093,7 +1093,7 @@
         <v>-1198.080000000001</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>95011.12</v>
@@ -1185,7 +1185,7 @@
         <v>-3391.830000000001</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>94526.73999999999</v>
@@ -1231,7 +1231,7 @@
         <v>-1132.559999999994</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>93394.17999999999</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>93394.17999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-77.22000000000958</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>94946.76999999999</v>
@@ -1461,7 +1461,7 @@
         <v>-1627.469999999996</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>93319.3</v>
@@ -1553,7 +1553,7 @@
         <v>-1196.910000000002</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>93265.48</v>
@@ -1645,7 +1645,7 @@
         <v>-1008.540000000001</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>98775.00999999999</v>
